--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.126.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.126.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.126.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.126.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -598,7 +598,7 @@
       <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>L98: localized OCR phrase divergence vs other OCR: "" vs "are hereby abolish xxx" :: That the printed Ã‡ases shall be and are hereby abolish- xxx.</t>
+          <t>L98: localized OCR phrase divergence vs other OCR: "" vs "are hereby abolish xxx" :: That the printed Çases shall be and are hereby abolish- xxx.</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L113: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L113: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]119</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]119</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L25: isolated marker/symbol line :: 119</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L14: isolated marker/symbol line :: 1</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]119</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -669,7 +673,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -679,7 +683,11 @@
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>L106: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -689,7 +697,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: %</t>
+          <t>L14: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -736,7 +744,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: F</t>
+          <t>L67: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -763,7 +771,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -783,7 +791,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L69: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -828,7 +836,11 @@
           <t>L92: isolated marker/symbol line :: ?</t>
         </is>
       </c>
-      <c r="O6" s="1" t="inlineStr"/>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>L106: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr"/>
@@ -911,7 +923,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L113: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L113: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -978,7 +990,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1017,7 +1029,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1056,7 +1068,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
